--- a/data/Everything.xlsx
+++ b/data/Everything.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Quiz\ZChineseP\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96CF043C-4BAE-4E0F-8F2E-B9427F2730B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BBDB926-E71C-4D5C-A2E2-8474EE441DCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13260" xr2:uid="{97CBE051-57A5-41E3-87DA-2837D7117692}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13260" activeTab="2" xr2:uid="{97CBE051-57A5-41E3-87DA-2837D7117692}"/>
   </bookViews>
   <sheets>
-    <sheet name="Words" sheetId="1" r:id="rId1"/>
+    <sheet name="WordsG5A" sheetId="1" r:id="rId1"/>
     <sheet name="WordLists" sheetId="2" r:id="rId2"/>
+    <sheet name="WordsG5B1-3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="402">
   <si>
     <t>拙</t>
   </si>
@@ -253,13 +254,1003 @@
   </si>
   <si>
     <t>四腳朝天</t>
+  </si>
+  <si>
+    <t>維持</t>
+  </si>
+  <si>
+    <t>拮据</t>
+  </si>
+  <si>
+    <t>誠實</t>
+  </si>
+  <si>
+    <t>精湛</t>
+  </si>
+  <si>
+    <t>器重</t>
+  </si>
+  <si>
+    <t>夢寐以求</t>
+  </si>
+  <si>
+    <t>嶄新</t>
+  </si>
+  <si>
+    <t>饋贈</t>
+  </si>
+  <si>
+    <t>嚴肅</t>
+  </si>
+  <si>
+    <t>悶悶不樂</t>
+  </si>
+  <si>
+    <t>道德</t>
+  </si>
+  <si>
+    <t>迷惑不解</t>
+  </si>
+  <si>
+    <t>號碼</t>
+  </si>
+  <si>
+    <t>辨別</t>
+  </si>
+  <si>
+    <t>痕跡</t>
+  </si>
+  <si>
+    <t>教誨</t>
+  </si>
+  <si>
+    <t>附近</t>
+  </si>
+  <si>
+    <t>劇烈</t>
+  </si>
+  <si>
+    <t>抖動</t>
+  </si>
+  <si>
+    <t>操縱</t>
+  </si>
+  <si>
+    <t>掙扎</t>
+  </si>
+  <si>
+    <t>筋疲力盡</t>
+  </si>
+  <si>
+    <t>距離</t>
+  </si>
+  <si>
+    <t>急切</t>
+  </si>
+  <si>
+    <t>爭辯</t>
+  </si>
+  <si>
+    <t>乞求</t>
+  </si>
+  <si>
+    <t>沮喪</t>
+  </si>
+  <si>
+    <t>誘惑</t>
+  </si>
+  <si>
+    <t>抉擇</t>
+  </si>
+  <si>
+    <t>告誡</t>
+  </si>
+  <si>
+    <t>實踐</t>
+  </si>
+  <si>
+    <t>嚴格</t>
+  </si>
+  <si>
+    <t>終生</t>
+  </si>
+  <si>
+    <t>蹤影</t>
+  </si>
+  <si>
+    <t>白茫茫</t>
+  </si>
+  <si>
+    <t>雲霧</t>
+  </si>
+  <si>
+    <t>專注</t>
+  </si>
+  <si>
+    <t>也許</t>
+  </si>
+  <si>
+    <t>籠罩</t>
+  </si>
+  <si>
+    <t>隱隱約約</t>
+  </si>
+  <si>
+    <t>輪廓</t>
+  </si>
+  <si>
+    <t>遮蓋</t>
+  </si>
+  <si>
+    <t>臉龐</t>
+  </si>
+  <si>
+    <t>熟悉</t>
+  </si>
+  <si>
+    <t>若隱若現</t>
+  </si>
+  <si>
+    <t>儀態萬千</t>
+  </si>
+  <si>
+    <t>怦然心動</t>
+  </si>
+  <si>
+    <t>由衷</t>
+  </si>
+  <si>
+    <t>和煦</t>
+  </si>
+  <si>
+    <t>沐浴</t>
+  </si>
+  <si>
+    <t>心曠神怡</t>
+  </si>
+  <si>
+    <t>聞名於世</t>
+  </si>
+  <si>
+    <t>天下奇觀</t>
+  </si>
+  <si>
+    <t>據説</t>
+  </si>
+  <si>
+    <t>寬闊</t>
+  </si>
+  <si>
+    <t>屹立</t>
+  </si>
+  <si>
+    <t>昂首</t>
+  </si>
+  <si>
+    <t>人聲鼎沸</t>
+  </si>
+  <si>
+    <t>風平浪靜</t>
+  </si>
+  <si>
+    <t>逐漸</t>
+  </si>
+  <si>
+    <t>橫貫</t>
+  </si>
+  <si>
+    <t>浩浩蕩蕩</t>
+  </si>
+  <si>
+    <t>山崩地裂</t>
+  </si>
+  <si>
+    <t>顫動</t>
+  </si>
+  <si>
+    <t>依舊</t>
+  </si>
+  <si>
+    <t>風號浪吼</t>
+  </si>
+  <si>
+    <t>嘆爲觀止</t>
+  </si>
+  <si>
+    <t>游覽</t>
+  </si>
+  <si>
+    <t>記載</t>
+  </si>
+  <si>
+    <t>修築</t>
+  </si>
+  <si>
+    <t>映襯</t>
+  </si>
+  <si>
+    <t>疏疏落落</t>
+  </si>
+  <si>
+    <t>眉飛色舞</t>
+  </si>
+  <si>
+    <t>亭亭玉立</t>
+  </si>
+  <si>
+    <t>巍然聳立</t>
+  </si>
+  <si>
+    <t>徒有虛名</t>
+  </si>
+  <si>
+    <t>政府</t>
+  </si>
+  <si>
+    <t>彌補</t>
+  </si>
+  <si>
+    <t>遺憾</t>
+  </si>
+  <si>
+    <t>行程</t>
+  </si>
+  <si>
+    <t>環繞</t>
+  </si>
+  <si>
+    <t>清幽淡雅</t>
+  </si>
+  <si>
+    <t>百看不厭</t>
+  </si>
+  <si>
+    <t>景致</t>
+  </si>
+  <si>
+    <t>美不勝收</t>
+  </si>
+  <si>
+    <t>流連忘返</t>
+  </si>
+  <si>
+    <t>背誦</t>
+  </si>
+  <si>
+    <t>波瀾壯闊</t>
+  </si>
+  <si>
+    <t>無暇</t>
+  </si>
+  <si>
+    <t>擴散</t>
+  </si>
+  <si>
+    <t>攀登</t>
+  </si>
+  <si>
+    <t>峰巒雄偉</t>
+  </si>
+  <si>
+    <t>拔地而起</t>
+  </si>
+  <si>
+    <t>奇峰羅列</t>
+  </si>
+  <si>
+    <t>屏障</t>
+  </si>
+  <si>
+    <t>栽倒</t>
+  </si>
+  <si>
+    <t>圍繞</t>
+  </si>
+  <si>
+    <t>倒映</t>
+  </si>
+  <si>
+    <t>連綿不斷</t>
+  </si>
+  <si>
+    <t>畫卷</t>
+  </si>
+  <si>
+    <t>捕</t>
+  </si>
+  <si>
+    <t>仰</t>
+  </si>
+  <si>
+    <t>碌</t>
+  </si>
+  <si>
+    <t>搜</t>
+  </si>
+  <si>
+    <t>介</t>
+  </si>
+  <si>
+    <t>瓶</t>
+  </si>
+  <si>
+    <t>懸</t>
+  </si>
+  <si>
+    <t>澤</t>
+  </si>
+  <si>
+    <t>守</t>
+  </si>
+  <si>
+    <t>綱</t>
+  </si>
+  <si>
+    <t>獵</t>
+  </si>
+  <si>
+    <t>液</t>
+  </si>
+  <si>
+    <t>骨碌碌</t>
+  </si>
+  <si>
+    <t>搜索</t>
+  </si>
+  <si>
+    <t>介紹</t>
+  </si>
+  <si>
+    <t>濃密</t>
+  </si>
+  <si>
+    <t>狹長</t>
+  </si>
+  <si>
+    <t>色澤</t>
+  </si>
+  <si>
+    <t>賞心悅目</t>
+  </si>
+  <si>
+    <t>守株待兔</t>
+  </si>
+  <si>
+    <t>自投羅網</t>
+  </si>
+  <si>
+    <t>獵物</t>
+  </si>
+  <si>
+    <t>誘捕</t>
+  </si>
+  <si>
+    <t>通常</t>
+  </si>
+  <si>
+    <t>強烈</t>
+  </si>
+  <si>
+    <t>養分</t>
+  </si>
+  <si>
+    <t>濃郁</t>
+  </si>
+  <si>
+    <t>甚至</t>
+  </si>
+  <si>
+    <t>屬</t>
+  </si>
+  <si>
+    <t>適</t>
+  </si>
+  <si>
+    <t>鋒</t>
+  </si>
+  <si>
+    <t>兇</t>
+  </si>
+  <si>
+    <t>撕</t>
+  </si>
+  <si>
+    <t>泉</t>
+  </si>
+  <si>
+    <t>潛</t>
+  </si>
+  <si>
+    <t>傾</t>
+  </si>
+  <si>
+    <t>斜</t>
+  </si>
+  <si>
+    <t>矮</t>
+  </si>
+  <si>
+    <t>幼</t>
+  </si>
+  <si>
+    <t>徵</t>
+  </si>
+  <si>
+    <t>寬敞</t>
+  </si>
+  <si>
+    <t>屬菸</t>
+  </si>
+  <si>
+    <t>哺乳</t>
+  </si>
+  <si>
+    <t>祖先</t>
+  </si>
+  <si>
+    <t>環境</t>
+  </si>
+  <si>
+    <t>退化</t>
+  </si>
+  <si>
+    <t>適應</t>
+  </si>
+  <si>
+    <t>鋒利</t>
+  </si>
+  <si>
+    <t>兇猛</t>
+  </si>
+  <si>
+    <t>噴泉</t>
+  </si>
+  <si>
+    <t>潛入</t>
+  </si>
+  <si>
+    <t>垂直</t>
+  </si>
+  <si>
+    <t>傾斜</t>
+  </si>
+  <si>
+    <t>特徵</t>
+  </si>
+  <si>
+    <t>壽命</t>
+  </si>
+  <si>
+    <t>鼠</t>
+  </si>
+  <si>
+    <t>馴</t>
+  </si>
+  <si>
+    <t>矯</t>
+  </si>
+  <si>
+    <t>玲</t>
+  </si>
+  <si>
+    <t>歇</t>
+  </si>
+  <si>
+    <t>豎</t>
+  </si>
+  <si>
+    <t>觸</t>
+  </si>
+  <si>
+    <t>縫</t>
+  </si>
+  <si>
+    <t>扒</t>
+  </si>
+  <si>
+    <t>編</t>
+  </si>
+  <si>
+    <t>勉</t>
+  </si>
+  <si>
+    <t>蔽</t>
+  </si>
+  <si>
+    <t>乖巧</t>
+  </si>
+  <si>
+    <t>馴良</t>
+  </si>
+  <si>
+    <t>矯健</t>
+  </si>
+  <si>
+    <t>玲瓏</t>
+  </si>
+  <si>
+    <t>格外</t>
+  </si>
+  <si>
+    <t>觸動</t>
+  </si>
+  <si>
+    <t>銳利</t>
+  </si>
+  <si>
+    <t>敏捷</t>
+  </si>
+  <si>
+    <t>縫隙</t>
+  </si>
+  <si>
+    <t>足夠</t>
+  </si>
+  <si>
+    <t>堅實</t>
+  </si>
+  <si>
+    <t>狹窄</t>
+  </si>
+  <si>
+    <t>勉強</t>
+  </si>
+  <si>
+    <t>遮蔽</t>
+  </si>
+  <si>
+    <t>梳理</t>
+  </si>
+  <si>
+    <t>蟄伏不動</t>
+  </si>
+  <si>
+    <t>連蹦帯跑</t>
+  </si>
+  <si>
+    <t>曬</t>
+  </si>
+  <si>
+    <t>際</t>
+  </si>
+  <si>
+    <t>鋼</t>
+  </si>
+  <si>
+    <t>殖</t>
+  </si>
+  <si>
+    <t>煤</t>
+  </si>
+  <si>
+    <t>炭</t>
+  </si>
+  <si>
+    <t>蒸</t>
+  </si>
+  <si>
+    <t>降</t>
+  </si>
+  <si>
+    <t>凝</t>
+  </si>
+  <si>
+    <t>菌</t>
+  </si>
+  <si>
+    <t>預</t>
+  </si>
+  <si>
+    <t>疾</t>
+  </si>
+  <si>
+    <t>傳説</t>
+  </si>
+  <si>
+    <t>寸草不生</t>
+  </si>
+  <si>
+    <t>實際</t>
+  </si>
+  <si>
+    <t>體積</t>
+  </si>
+  <si>
+    <t>鋼鐵</t>
+  </si>
+  <si>
+    <t>關係</t>
+  </si>
+  <si>
+    <t>密切</t>
+  </si>
+  <si>
+    <t>生存</t>
+  </si>
+  <si>
+    <t>繁殖</t>
+  </si>
+  <si>
+    <t>糧食</t>
+  </si>
+  <si>
+    <t>下降</t>
+  </si>
+  <si>
+    <t>流動</t>
+  </si>
+  <si>
+    <t>殺菌</t>
+  </si>
+  <si>
+    <t>預防</t>
+  </si>
+  <si>
+    <t>治療</t>
+  </si>
+  <si>
+    <t>疾病</t>
+  </si>
+  <si>
+    <t>召</t>
+  </si>
+  <si>
+    <t>缺</t>
+  </si>
+  <si>
+    <t>允</t>
+  </si>
+  <si>
+    <t>典</t>
+  </si>
+  <si>
+    <t>欺</t>
+  </si>
+  <si>
+    <t>慮</t>
+  </si>
+  <si>
+    <t>辭</t>
+  </si>
+  <si>
+    <t>拒</t>
+  </si>
+  <si>
+    <t>斥</t>
+  </si>
+  <si>
+    <t>職</t>
+  </si>
+  <si>
+    <t>削</t>
+  </si>
+  <si>
+    <t>協</t>
+  </si>
+  <si>
+    <t>進</t>
+  </si>
+  <si>
+    <t>攻</t>
+  </si>
+  <si>
+    <t>無價之寳</t>
+  </si>
+  <si>
+    <t>召集</t>
+  </si>
+  <si>
+    <t>商議</t>
+  </si>
+  <si>
+    <t>機智</t>
+  </si>
+  <si>
+    <t>理虧</t>
+  </si>
+  <si>
+    <t>完好無缺</t>
+  </si>
+  <si>
+    <t>絕口不提</t>
+  </si>
+  <si>
+    <t>怒髮衝冠</t>
+  </si>
+  <si>
+    <t>承諾</t>
+  </si>
+  <si>
+    <t>得罪</t>
+  </si>
+  <si>
+    <t>推辭</t>
+  </si>
+  <si>
+    <t>擅長</t>
+  </si>
+  <si>
+    <t>同歸菸盡</t>
+  </si>
+  <si>
+    <t>怒目圄睜</t>
+  </si>
+  <si>
+    <t>毫不示弱</t>
+  </si>
+  <si>
+    <t>削弱</t>
+  </si>
+  <si>
+    <t>利益</t>
+  </si>
+  <si>
+    <t>同心協力</t>
+  </si>
+  <si>
+    <t>保衛</t>
+  </si>
+  <si>
+    <t>懼</t>
+  </si>
+  <si>
+    <t>迫</t>
+  </si>
+  <si>
+    <t>辱</t>
+  </si>
+  <si>
+    <t>屑</t>
+  </si>
+  <si>
+    <t>謙</t>
+  </si>
+  <si>
+    <t>討</t>
+  </si>
+  <si>
+    <t>侵</t>
+  </si>
+  <si>
+    <t>崇</t>
+  </si>
+  <si>
+    <t>批</t>
+  </si>
+  <si>
+    <t>愧</t>
+  </si>
+  <si>
+    <t>振</t>
+  </si>
+  <si>
+    <t>榮</t>
+  </si>
+  <si>
+    <t>威迫</t>
+  </si>
+  <si>
+    <t>羞辱</t>
+  </si>
+  <si>
+    <t>屢立戰功</t>
+  </si>
+  <si>
+    <t>傲慢</t>
+  </si>
+  <si>
+    <t>忍無可忍</t>
+  </si>
+  <si>
+    <t>不屑</t>
+  </si>
+  <si>
+    <t>阻止</t>
+  </si>
+  <si>
+    <t>謙讓</t>
+  </si>
+  <si>
+    <t>揚長而去</t>
+  </si>
+  <si>
+    <t>侵犯</t>
+  </si>
+  <si>
+    <t>戰績顯赫</t>
+  </si>
+  <si>
+    <t>忠心耿耿</t>
+  </si>
+  <si>
+    <t>崇拜</t>
+  </si>
+  <si>
+    <t>計較</t>
+  </si>
+  <si>
+    <t>囉嗦</t>
+  </si>
+  <si>
+    <t>慚愧</t>
+  </si>
+  <si>
+    <t>吩咐</t>
+  </si>
+  <si>
+    <t>繁榮昌盛</t>
+  </si>
+  <si>
+    <t>將</t>
+  </si>
+  <si>
+    <t>嬴</t>
+  </si>
+  <si>
+    <t>勝</t>
+  </si>
+  <si>
+    <t>肯</t>
+  </si>
+  <si>
+    <t>難</t>
+  </si>
+  <si>
+    <t>胸</t>
+  </si>
+  <si>
+    <t>惑</t>
+  </si>
+  <si>
+    <t>則</t>
+  </si>
+  <si>
+    <t>输</t>
+  </si>
+  <si>
+    <t>整</t>
+  </si>
+  <si>
+    <t>序</t>
+  </si>
+  <si>
+    <t>敗</t>
+  </si>
+  <si>
+    <t>才能</t>
+  </si>
+  <si>
+    <t>將軍</t>
+  </si>
+  <si>
+    <t>勝利</t>
+  </si>
+  <si>
+    <t>當然</t>
+  </si>
+  <si>
+    <t>為難</t>
+  </si>
+  <si>
+    <t>胸有成竹</t>
+  </si>
+  <si>
+    <t>疑惑</t>
+  </si>
+  <si>
+    <t>規則</t>
+  </si>
+  <si>
+    <t>淡定</t>
+  </si>
+  <si>
+    <t>遙遙領先</t>
+  </si>
+  <si>
+    <t>信服</t>
+  </si>
+  <si>
+    <t>調整</t>
+  </si>
+  <si>
+    <t>順序</t>
+  </si>
+  <si>
+    <t>反敗為勝</t>
+  </si>
+  <si>
+    <t>訪</t>
+  </si>
+  <si>
+    <t>仗</t>
+  </si>
+  <si>
+    <t>侮</t>
+  </si>
+  <si>
+    <t>夥</t>
+  </si>
+  <si>
+    <t>謊</t>
+  </si>
+  <si>
+    <t>拱</t>
+  </si>
+  <si>
+    <t>矩</t>
+  </si>
+  <si>
+    <t>席</t>
+  </si>
+  <si>
+    <t>業</t>
+  </si>
+  <si>
+    <t>勞</t>
+  </si>
+  <si>
+    <t>賊</t>
+  </si>
+  <si>
+    <t>尊</t>
+  </si>
+  <si>
+    <t>訪問</t>
+  </si>
+  <si>
+    <t>國勢強盛</t>
+  </si>
+  <si>
+    <t>侮辱</t>
+  </si>
+  <si>
+    <t>威風</t>
+  </si>
+  <si>
+    <t>到底</t>
+  </si>
+  <si>
+    <t>迎接</t>
+  </si>
+  <si>
+    <t>打發</t>
+  </si>
+  <si>
+    <t>規矩</t>
+  </si>
+  <si>
+    <t>招待</t>
+  </si>
+  <si>
+    <t>盜竊</t>
+  </si>
+  <si>
+    <t>沒出息</t>
+  </si>
+  <si>
+    <t>得意揚揚</t>
+  </si>
+  <si>
+    <t>面不改色</t>
+  </si>
+  <si>
+    <t>安居樂業</t>
+  </si>
+  <si>
+    <t>勞動</t>
+  </si>
+  <si>
+    <t>取笑</t>
+  </si>
+  <si>
+    <t>尊重</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -272,6 +1263,12 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="楷体"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -294,9 +1291,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -631,7 +1629,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BD7761B-4BFF-4633-8F81-F9821C6B14BA}">
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D160"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
@@ -1099,7 +2097,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34">
-        <f t="shared" ref="A34:A60" si="0">A33+1</f>
+        <f t="shared" ref="A34:A97" si="0">A33+1</f>
         <v>33</v>
       </c>
       <c r="B34" t="s">
@@ -1499,6 +2497,1506 @@
         <v>2</v>
       </c>
       <c r="D60">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>72</v>
+      </c>
+      <c r="C61">
+        <v>3</v>
+      </c>
+      <c r="D61">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>73</v>
+      </c>
+      <c r="C62">
+        <v>3</v>
+      </c>
+      <c r="D62">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>74</v>
+      </c>
+      <c r="C63">
+        <v>3</v>
+      </c>
+      <c r="D63">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>75</v>
+      </c>
+      <c r="C64">
+        <v>3</v>
+      </c>
+      <c r="D64">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>76</v>
+      </c>
+      <c r="C65">
+        <v>3</v>
+      </c>
+      <c r="D65">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>77</v>
+      </c>
+      <c r="C66">
+        <v>3</v>
+      </c>
+      <c r="D66">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <f t="shared" si="0"/>
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>78</v>
+      </c>
+      <c r="C67">
+        <v>3</v>
+      </c>
+      <c r="D67">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <f t="shared" si="0"/>
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>79</v>
+      </c>
+      <c r="C68">
+        <v>3</v>
+      </c>
+      <c r="D68">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <f t="shared" si="0"/>
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>80</v>
+      </c>
+      <c r="C69">
+        <v>3</v>
+      </c>
+      <c r="D69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <f t="shared" si="0"/>
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>81</v>
+      </c>
+      <c r="C70">
+        <v>3</v>
+      </c>
+      <c r="D70">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A71">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>82</v>
+      </c>
+      <c r="C71">
+        <v>3</v>
+      </c>
+      <c r="D71">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A72">
+        <f t="shared" si="0"/>
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>83</v>
+      </c>
+      <c r="C72">
+        <v>3</v>
+      </c>
+      <c r="D72">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A73">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>84</v>
+      </c>
+      <c r="C73">
+        <v>3</v>
+      </c>
+      <c r="D73">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A74">
+        <f t="shared" si="0"/>
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>85</v>
+      </c>
+      <c r="C74">
+        <v>3</v>
+      </c>
+      <c r="D74">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A75">
+        <f t="shared" si="0"/>
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>86</v>
+      </c>
+      <c r="C75">
+        <v>3</v>
+      </c>
+      <c r="D75">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A76">
+        <f t="shared" si="0"/>
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>87</v>
+      </c>
+      <c r="C76">
+        <v>3</v>
+      </c>
+      <c r="D76">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A77">
+        <f t="shared" si="0"/>
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>88</v>
+      </c>
+      <c r="C77">
+        <v>4</v>
+      </c>
+      <c r="D77">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A78">
+        <f t="shared" si="0"/>
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>89</v>
+      </c>
+      <c r="C78">
+        <v>4</v>
+      </c>
+      <c r="D78">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A79">
+        <f t="shared" si="0"/>
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>90</v>
+      </c>
+      <c r="C79">
+        <v>4</v>
+      </c>
+      <c r="D79">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A80">
+        <f t="shared" si="0"/>
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>91</v>
+      </c>
+      <c r="C80">
+        <v>4</v>
+      </c>
+      <c r="D80">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A81">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>92</v>
+      </c>
+      <c r="C81">
+        <v>4</v>
+      </c>
+      <c r="D81">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A82">
+        <f t="shared" si="0"/>
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>93</v>
+      </c>
+      <c r="C82">
+        <v>4</v>
+      </c>
+      <c r="D82">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A83">
+        <f t="shared" si="0"/>
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>94</v>
+      </c>
+      <c r="C83">
+        <v>4</v>
+      </c>
+      <c r="D83">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A84">
+        <f t="shared" si="0"/>
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>95</v>
+      </c>
+      <c r="C84">
+        <v>4</v>
+      </c>
+      <c r="D84">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A85">
+        <f t="shared" si="0"/>
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
+        <v>96</v>
+      </c>
+      <c r="C85">
+        <v>4</v>
+      </c>
+      <c r="D85">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A86">
+        <f t="shared" si="0"/>
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
+        <v>97</v>
+      </c>
+      <c r="C86">
+        <v>4</v>
+      </c>
+      <c r="D86">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A87">
+        <f t="shared" si="0"/>
+        <v>86</v>
+      </c>
+      <c r="B87" t="s">
+        <v>98</v>
+      </c>
+      <c r="C87">
+        <v>4</v>
+      </c>
+      <c r="D87">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A88">
+        <f t="shared" si="0"/>
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>99</v>
+      </c>
+      <c r="C88">
+        <v>4</v>
+      </c>
+      <c r="D88">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A89">
+        <f t="shared" si="0"/>
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
+        <v>100</v>
+      </c>
+      <c r="C89">
+        <v>4</v>
+      </c>
+      <c r="D89">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A90">
+        <f t="shared" si="0"/>
+        <v>89</v>
+      </c>
+      <c r="B90" t="s">
+        <v>101</v>
+      </c>
+      <c r="C90">
+        <v>4</v>
+      </c>
+      <c r="D90">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A91">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+      <c r="B91" t="s">
+        <v>102</v>
+      </c>
+      <c r="C91">
+        <v>4</v>
+      </c>
+      <c r="D91">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A92">
+        <f t="shared" si="0"/>
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
+        <v>103</v>
+      </c>
+      <c r="C92">
+        <v>4</v>
+      </c>
+      <c r="D92">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A93">
+        <f t="shared" si="0"/>
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
+        <v>104</v>
+      </c>
+      <c r="C93">
+        <v>4</v>
+      </c>
+      <c r="D93">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A94">
+        <f t="shared" si="0"/>
+        <v>93</v>
+      </c>
+      <c r="B94" t="s">
+        <v>105</v>
+      </c>
+      <c r="C94">
+        <v>5</v>
+      </c>
+      <c r="D94">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A95">
+        <f t="shared" si="0"/>
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
+        <v>106</v>
+      </c>
+      <c r="C95">
+        <v>5</v>
+      </c>
+      <c r="D95">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A96">
+        <f t="shared" si="0"/>
+        <v>95</v>
+      </c>
+      <c r="B96" t="s">
+        <v>107</v>
+      </c>
+      <c r="C96">
+        <v>5</v>
+      </c>
+      <c r="D96">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A97">
+        <f t="shared" si="0"/>
+        <v>96</v>
+      </c>
+      <c r="B97" t="s">
+        <v>108</v>
+      </c>
+      <c r="C97">
+        <v>5</v>
+      </c>
+      <c r="D97">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A98">
+        <f t="shared" ref="A98:A160" si="1">A97+1</f>
+        <v>97</v>
+      </c>
+      <c r="B98" t="s">
+        <v>109</v>
+      </c>
+      <c r="C98">
+        <v>5</v>
+      </c>
+      <c r="D98">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A99">
+        <f t="shared" si="1"/>
+        <v>98</v>
+      </c>
+      <c r="B99" t="s">
+        <v>110</v>
+      </c>
+      <c r="C99">
+        <v>5</v>
+      </c>
+      <c r="D99">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A100">
+        <f t="shared" si="1"/>
+        <v>99</v>
+      </c>
+      <c r="B100" t="s">
+        <v>111</v>
+      </c>
+      <c r="C100">
+        <v>5</v>
+      </c>
+      <c r="D100">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A101">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="B101" t="s">
+        <v>112</v>
+      </c>
+      <c r="C101">
+        <v>5</v>
+      </c>
+      <c r="D101">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A102">
+        <f t="shared" si="1"/>
+        <v>101</v>
+      </c>
+      <c r="B102" t="s">
+        <v>113</v>
+      </c>
+      <c r="C102">
+        <v>5</v>
+      </c>
+      <c r="D102">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A103">
+        <f t="shared" si="1"/>
+        <v>102</v>
+      </c>
+      <c r="B103" t="s">
+        <v>114</v>
+      </c>
+      <c r="C103">
+        <v>5</v>
+      </c>
+      <c r="D103">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A104">
+        <f t="shared" si="1"/>
+        <v>103</v>
+      </c>
+      <c r="B104" t="s">
+        <v>115</v>
+      </c>
+      <c r="C104">
+        <v>5</v>
+      </c>
+      <c r="D104">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A105">
+        <f t="shared" si="1"/>
+        <v>104</v>
+      </c>
+      <c r="B105" t="s">
+        <v>116</v>
+      </c>
+      <c r="C105">
+        <v>5</v>
+      </c>
+      <c r="D105">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A106">
+        <f t="shared" si="1"/>
+        <v>105</v>
+      </c>
+      <c r="B106" t="s">
+        <v>117</v>
+      </c>
+      <c r="C106">
+        <v>5</v>
+      </c>
+      <c r="D106">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A107">
+        <f t="shared" si="1"/>
+        <v>106</v>
+      </c>
+      <c r="B107" t="s">
+        <v>118</v>
+      </c>
+      <c r="C107">
+        <v>5</v>
+      </c>
+      <c r="D107">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A108">
+        <f t="shared" si="1"/>
+        <v>107</v>
+      </c>
+      <c r="B108" t="s">
+        <v>119</v>
+      </c>
+      <c r="C108">
+        <v>5</v>
+      </c>
+      <c r="D108">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A109">
+        <f t="shared" si="1"/>
+        <v>108</v>
+      </c>
+      <c r="B109" t="s">
+        <v>120</v>
+      </c>
+      <c r="C109">
+        <v>5</v>
+      </c>
+      <c r="D109">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A110">
+        <f t="shared" si="1"/>
+        <v>109</v>
+      </c>
+      <c r="B110" t="s">
+        <v>121</v>
+      </c>
+      <c r="C110">
+        <v>5</v>
+      </c>
+      <c r="D110">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A111">
+        <f t="shared" si="1"/>
+        <v>110</v>
+      </c>
+      <c r="B111" t="s">
+        <v>122</v>
+      </c>
+      <c r="C111">
+        <v>5</v>
+      </c>
+      <c r="D111">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A112">
+        <f t="shared" si="1"/>
+        <v>111</v>
+      </c>
+      <c r="B112" t="s">
+        <v>123</v>
+      </c>
+      <c r="C112">
+        <v>6</v>
+      </c>
+      <c r="D112">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A113">
+        <f t="shared" si="1"/>
+        <v>112</v>
+      </c>
+      <c r="B113" t="s">
+        <v>124</v>
+      </c>
+      <c r="C113">
+        <v>6</v>
+      </c>
+      <c r="D113">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A114">
+        <f t="shared" si="1"/>
+        <v>113</v>
+      </c>
+      <c r="B114" t="s">
+        <v>125</v>
+      </c>
+      <c r="C114">
+        <v>6</v>
+      </c>
+      <c r="D114">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A115">
+        <f t="shared" si="1"/>
+        <v>114</v>
+      </c>
+      <c r="B115" t="s">
+        <v>126</v>
+      </c>
+      <c r="C115">
+        <v>6</v>
+      </c>
+      <c r="D115">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A116">
+        <f t="shared" si="1"/>
+        <v>115</v>
+      </c>
+      <c r="B116" t="s">
+        <v>127</v>
+      </c>
+      <c r="C116">
+        <v>6</v>
+      </c>
+      <c r="D116">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A117">
+        <f t="shared" si="1"/>
+        <v>116</v>
+      </c>
+      <c r="B117" t="s">
+        <v>128</v>
+      </c>
+      <c r="C117">
+        <v>6</v>
+      </c>
+      <c r="D117">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A118">
+        <f t="shared" si="1"/>
+        <v>117</v>
+      </c>
+      <c r="B118" t="s">
+        <v>129</v>
+      </c>
+      <c r="C118">
+        <v>6</v>
+      </c>
+      <c r="D118">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A119">
+        <f t="shared" si="1"/>
+        <v>118</v>
+      </c>
+      <c r="B119" t="s">
+        <v>130</v>
+      </c>
+      <c r="C119">
+        <v>6</v>
+      </c>
+      <c r="D119">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A120">
+        <f t="shared" si="1"/>
+        <v>119</v>
+      </c>
+      <c r="B120" t="s">
+        <v>131</v>
+      </c>
+      <c r="C120">
+        <v>6</v>
+      </c>
+      <c r="D120">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A121">
+        <f t="shared" si="1"/>
+        <v>120</v>
+      </c>
+      <c r="B121" t="s">
+        <v>132</v>
+      </c>
+      <c r="C121">
+        <v>6</v>
+      </c>
+      <c r="D121">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A122">
+        <f t="shared" si="1"/>
+        <v>121</v>
+      </c>
+      <c r="B122" t="s">
+        <v>133</v>
+      </c>
+      <c r="C122">
+        <v>6</v>
+      </c>
+      <c r="D122">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A123">
+        <f t="shared" si="1"/>
+        <v>122</v>
+      </c>
+      <c r="B123" t="s">
+        <v>134</v>
+      </c>
+      <c r="C123">
+        <v>6</v>
+      </c>
+      <c r="D123">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A124">
+        <f t="shared" si="1"/>
+        <v>123</v>
+      </c>
+      <c r="B124" t="s">
+        <v>135</v>
+      </c>
+      <c r="C124">
+        <v>6</v>
+      </c>
+      <c r="D124">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A125">
+        <f t="shared" si="1"/>
+        <v>124</v>
+      </c>
+      <c r="B125" t="s">
+        <v>136</v>
+      </c>
+      <c r="C125">
+        <v>6</v>
+      </c>
+      <c r="D125">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A126">
+        <f t="shared" si="1"/>
+        <v>125</v>
+      </c>
+      <c r="B126" t="s">
+        <v>137</v>
+      </c>
+      <c r="C126">
+        <v>6</v>
+      </c>
+      <c r="D126">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A127">
+        <f t="shared" si="1"/>
+        <v>126</v>
+      </c>
+      <c r="B127" t="s">
+        <v>138</v>
+      </c>
+      <c r="C127">
+        <v>6</v>
+      </c>
+      <c r="D127">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A128">
+        <f t="shared" si="1"/>
+        <v>127</v>
+      </c>
+      <c r="B128" t="s">
+        <v>139</v>
+      </c>
+      <c r="C128">
+        <v>7</v>
+      </c>
+      <c r="D128">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A129">
+        <f t="shared" si="1"/>
+        <v>128</v>
+      </c>
+      <c r="B129" t="s">
+        <v>140</v>
+      </c>
+      <c r="C129">
+        <v>7</v>
+      </c>
+      <c r="D129">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A130">
+        <f t="shared" si="1"/>
+        <v>129</v>
+      </c>
+      <c r="B130" t="s">
+        <v>141</v>
+      </c>
+      <c r="C130">
+        <v>7</v>
+      </c>
+      <c r="D130">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A131">
+        <f t="shared" si="1"/>
+        <v>130</v>
+      </c>
+      <c r="B131" t="s">
+        <v>142</v>
+      </c>
+      <c r="C131">
+        <v>7</v>
+      </c>
+      <c r="D131">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A132">
+        <f t="shared" si="1"/>
+        <v>131</v>
+      </c>
+      <c r="B132" t="s">
+        <v>143</v>
+      </c>
+      <c r="C132">
+        <v>7</v>
+      </c>
+      <c r="D132">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A133">
+        <f t="shared" si="1"/>
+        <v>132</v>
+      </c>
+      <c r="B133" t="s">
+        <v>144</v>
+      </c>
+      <c r="C133">
+        <v>7</v>
+      </c>
+      <c r="D133">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A134">
+        <f t="shared" si="1"/>
+        <v>133</v>
+      </c>
+      <c r="B134" t="s">
+        <v>145</v>
+      </c>
+      <c r="C134">
+        <v>7</v>
+      </c>
+      <c r="D134">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A135">
+        <f t="shared" si="1"/>
+        <v>134</v>
+      </c>
+      <c r="B135" t="s">
+        <v>146</v>
+      </c>
+      <c r="C135">
+        <v>7</v>
+      </c>
+      <c r="D135">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A136">
+        <f t="shared" si="1"/>
+        <v>135</v>
+      </c>
+      <c r="B136" t="s">
+        <v>147</v>
+      </c>
+      <c r="C136">
+        <v>7</v>
+      </c>
+      <c r="D136">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A137">
+        <f t="shared" si="1"/>
+        <v>136</v>
+      </c>
+      <c r="B137" t="s">
+        <v>148</v>
+      </c>
+      <c r="C137">
+        <v>7</v>
+      </c>
+      <c r="D137">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A138">
+        <f t="shared" si="1"/>
+        <v>137</v>
+      </c>
+      <c r="B138" t="s">
+        <v>149</v>
+      </c>
+      <c r="C138">
+        <v>7</v>
+      </c>
+      <c r="D138">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A139">
+        <f t="shared" si="1"/>
+        <v>138</v>
+      </c>
+      <c r="B139" t="s">
+        <v>150</v>
+      </c>
+      <c r="C139">
+        <v>7</v>
+      </c>
+      <c r="D139">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A140">
+        <f t="shared" si="1"/>
+        <v>139</v>
+      </c>
+      <c r="B140" t="s">
+        <v>151</v>
+      </c>
+      <c r="C140">
+        <v>7</v>
+      </c>
+      <c r="D140">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A141">
+        <f t="shared" si="1"/>
+        <v>140</v>
+      </c>
+      <c r="B141" t="s">
+        <v>152</v>
+      </c>
+      <c r="C141">
+        <v>7</v>
+      </c>
+      <c r="D141">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A142">
+        <f t="shared" si="1"/>
+        <v>141</v>
+      </c>
+      <c r="B142" t="s">
+        <v>153</v>
+      </c>
+      <c r="C142">
+        <v>7</v>
+      </c>
+      <c r="D142">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A143">
+        <f t="shared" si="1"/>
+        <v>142</v>
+      </c>
+      <c r="B143" t="s">
+        <v>154</v>
+      </c>
+      <c r="C143">
+        <v>7</v>
+      </c>
+      <c r="D143">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A144">
+        <f t="shared" si="1"/>
+        <v>143</v>
+      </c>
+      <c r="B144" t="s">
+        <v>155</v>
+      </c>
+      <c r="C144">
+        <v>7</v>
+      </c>
+      <c r="D144">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A145">
+        <f t="shared" si="1"/>
+        <v>144</v>
+      </c>
+      <c r="B145" t="s">
+        <v>156</v>
+      </c>
+      <c r="C145">
+        <v>7</v>
+      </c>
+      <c r="D145">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A146">
+        <f t="shared" si="1"/>
+        <v>145</v>
+      </c>
+      <c r="B146" t="s">
+        <v>157</v>
+      </c>
+      <c r="C146">
+        <v>7</v>
+      </c>
+      <c r="D146">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A147">
+        <f t="shared" si="1"/>
+        <v>146</v>
+      </c>
+      <c r="B147" t="s">
+        <v>158</v>
+      </c>
+      <c r="C147">
+        <v>7</v>
+      </c>
+      <c r="D147">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A148">
+        <f t="shared" si="1"/>
+        <v>147</v>
+      </c>
+      <c r="B148" t="s">
+        <v>159</v>
+      </c>
+      <c r="C148">
+        <v>8</v>
+      </c>
+      <c r="D148">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A149">
+        <f t="shared" si="1"/>
+        <v>148</v>
+      </c>
+      <c r="B149" t="s">
+        <v>160</v>
+      </c>
+      <c r="C149">
+        <v>8</v>
+      </c>
+      <c r="D149">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A150">
+        <f t="shared" si="1"/>
+        <v>149</v>
+      </c>
+      <c r="B150" t="s">
+        <v>161</v>
+      </c>
+      <c r="C150">
+        <v>8</v>
+      </c>
+      <c r="D150">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A151">
+        <f t="shared" si="1"/>
+        <v>150</v>
+      </c>
+      <c r="B151" t="s">
+        <v>162</v>
+      </c>
+      <c r="C151">
+        <v>8</v>
+      </c>
+      <c r="D151">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A152">
+        <f t="shared" si="1"/>
+        <v>151</v>
+      </c>
+      <c r="B152" t="s">
+        <v>163</v>
+      </c>
+      <c r="C152">
+        <v>8</v>
+      </c>
+      <c r="D152">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A153">
+        <f t="shared" si="1"/>
+        <v>152</v>
+      </c>
+      <c r="B153" t="s">
+        <v>164</v>
+      </c>
+      <c r="C153">
+        <v>8</v>
+      </c>
+      <c r="D153">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A154">
+        <f t="shared" si="1"/>
+        <v>153</v>
+      </c>
+      <c r="B154" t="s">
+        <v>165</v>
+      </c>
+      <c r="C154">
+        <v>8</v>
+      </c>
+      <c r="D154">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A155">
+        <f t="shared" si="1"/>
+        <v>154</v>
+      </c>
+      <c r="B155" t="s">
+        <v>166</v>
+      </c>
+      <c r="C155">
+        <v>8</v>
+      </c>
+      <c r="D155">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A156">
+        <f t="shared" si="1"/>
+        <v>155</v>
+      </c>
+      <c r="B156" t="s">
+        <v>167</v>
+      </c>
+      <c r="C156">
+        <v>8</v>
+      </c>
+      <c r="D156">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A157">
+        <f t="shared" si="1"/>
+        <v>156</v>
+      </c>
+      <c r="B157" t="s">
+        <v>168</v>
+      </c>
+      <c r="C157">
+        <v>8</v>
+      </c>
+      <c r="D157">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A158">
+        <f t="shared" si="1"/>
+        <v>157</v>
+      </c>
+      <c r="B158" t="s">
+        <v>169</v>
+      </c>
+      <c r="C158">
+        <v>8</v>
+      </c>
+      <c r="D158">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A159">
+        <f t="shared" si="1"/>
+        <v>158</v>
+      </c>
+      <c r="B159" t="s">
+        <v>170</v>
+      </c>
+      <c r="C159">
+        <v>8</v>
+      </c>
+      <c r="D159">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A160">
+        <f t="shared" si="1"/>
+        <v>159</v>
+      </c>
+      <c r="B160" t="s">
+        <v>171</v>
+      </c>
+      <c r="C160">
+        <v>8</v>
+      </c>
+      <c r="D160">
         <v>2</v>
       </c>
     </row>
@@ -1587,4 +4085,3529 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EDAFB06-9329-406B-9428-A1B32E2D54BA}">
+  <dimension ref="A1:Q233"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="9" max="9" width="22.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="15" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="15" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="15" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="15" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" ht="15" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="15" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" ht="15" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" ht="15" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" ht="15" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" ht="15" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" ht="15" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" ht="15" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" ht="15" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C29">
+        <v>2</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="I29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="2"/>
+    </row>
+    <row r="30" spans="1:17" ht="15" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="I30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="2"/>
+    </row>
+    <row r="31" spans="1:17" ht="15" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C31">
+        <v>2</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="I31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="2"/>
+    </row>
+    <row r="32" spans="1:17" ht="15" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C32">
+        <v>2</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="I32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" s="2"/>
+      <c r="Q32" s="2"/>
+    </row>
+    <row r="33" spans="1:17" ht="15" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <f>A32+1</f>
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C33">
+        <v>2</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="I33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" s="2"/>
+      <c r="Q33" s="2"/>
+    </row>
+    <row r="34" spans="1:17" ht="15" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <f t="shared" ref="A34:A97" si="0">A33+1</f>
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C34">
+        <v>2</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="I34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2"/>
+    </row>
+    <row r="35" spans="1:17" ht="15" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C35">
+        <v>2</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" ht="15" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C36">
+        <v>2</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" ht="15" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C37">
+        <v>2</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" ht="15" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C38">
+        <v>2</v>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" ht="15" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C39">
+        <v>2</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" ht="15" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C40">
+        <v>2</v>
+      </c>
+      <c r="D40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" ht="15" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C41">
+        <v>2</v>
+      </c>
+      <c r="D41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" ht="15" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C42">
+        <v>2</v>
+      </c>
+      <c r="D42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" ht="15" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C43">
+        <v>2</v>
+      </c>
+      <c r="D43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" ht="15" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C44">
+        <v>2</v>
+      </c>
+      <c r="D44">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" ht="15" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C45">
+        <v>2</v>
+      </c>
+      <c r="D45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" ht="15" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C46">
+        <v>2</v>
+      </c>
+      <c r="D46">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" ht="15" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C47">
+        <v>2</v>
+      </c>
+      <c r="D47">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" ht="15" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C48">
+        <v>2</v>
+      </c>
+      <c r="D48">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C49">
+        <v>2</v>
+      </c>
+      <c r="D49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C50">
+        <v>2</v>
+      </c>
+      <c r="D50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C51">
+        <v>2</v>
+      </c>
+      <c r="D51">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C52">
+        <v>2</v>
+      </c>
+      <c r="D52">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C53">
+        <v>2</v>
+      </c>
+      <c r="D53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C54">
+        <v>2</v>
+      </c>
+      <c r="D54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C55">
+        <v>2</v>
+      </c>
+      <c r="D55">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C56">
+        <v>2</v>
+      </c>
+      <c r="D56">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C57">
+        <v>3</v>
+      </c>
+      <c r="D57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C58">
+        <v>3</v>
+      </c>
+      <c r="D58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C59">
+        <v>3</v>
+      </c>
+      <c r="D59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C60">
+        <v>3</v>
+      </c>
+      <c r="D60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C61">
+        <v>3</v>
+      </c>
+      <c r="D61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C62">
+        <v>3</v>
+      </c>
+      <c r="D62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C63">
+        <v>3</v>
+      </c>
+      <c r="D63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C64">
+        <v>3</v>
+      </c>
+      <c r="D64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C65">
+        <v>3</v>
+      </c>
+      <c r="D65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C66">
+        <v>3</v>
+      </c>
+      <c r="D66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <f t="shared" si="0"/>
+        <v>66</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C67">
+        <v>3</v>
+      </c>
+      <c r="D67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <f t="shared" si="0"/>
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C68">
+        <v>3</v>
+      </c>
+      <c r="D68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <f t="shared" si="0"/>
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C69">
+        <v>3</v>
+      </c>
+      <c r="D69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <f t="shared" si="0"/>
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C70">
+        <v>3</v>
+      </c>
+      <c r="D70">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A71">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C71">
+        <v>3</v>
+      </c>
+      <c r="D71">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A72">
+        <f t="shared" si="0"/>
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C72">
+        <v>3</v>
+      </c>
+      <c r="D72">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A73">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C73">
+        <v>3</v>
+      </c>
+      <c r="D73">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A74">
+        <f t="shared" si="0"/>
+        <v>73</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C74">
+        <v>3</v>
+      </c>
+      <c r="D74">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A75">
+        <f t="shared" si="0"/>
+        <v>74</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C75">
+        <v>3</v>
+      </c>
+      <c r="D75">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A76">
+        <f t="shared" si="0"/>
+        <v>75</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C76">
+        <v>3</v>
+      </c>
+      <c r="D76">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A77">
+        <f t="shared" si="0"/>
+        <v>76</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C77">
+        <v>3</v>
+      </c>
+      <c r="D77">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A78">
+        <f t="shared" si="0"/>
+        <v>77</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C78">
+        <v>3</v>
+      </c>
+      <c r="D78">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A79">
+        <f t="shared" si="0"/>
+        <v>78</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C79">
+        <v>3</v>
+      </c>
+      <c r="D79">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A80">
+        <f t="shared" si="0"/>
+        <v>79</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C80">
+        <v>3</v>
+      </c>
+      <c r="D80">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A81">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C81">
+        <v>3</v>
+      </c>
+      <c r="D81">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A82">
+        <f t="shared" si="0"/>
+        <v>81</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C82">
+        <v>3</v>
+      </c>
+      <c r="D82">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A83">
+        <f t="shared" si="0"/>
+        <v>82</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C83">
+        <v>3</v>
+      </c>
+      <c r="D83">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A84">
+        <f t="shared" si="0"/>
+        <v>83</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C84">
+        <v>3</v>
+      </c>
+      <c r="D84">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A85">
+        <f t="shared" si="0"/>
+        <v>84</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C85">
+        <v>3</v>
+      </c>
+      <c r="D85">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A86">
+        <f t="shared" si="0"/>
+        <v>85</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C86">
+        <v>3</v>
+      </c>
+      <c r="D86">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A87">
+        <f t="shared" si="0"/>
+        <v>86</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C87">
+        <v>4</v>
+      </c>
+      <c r="D87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A88">
+        <f t="shared" si="0"/>
+        <v>87</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C88">
+        <v>4</v>
+      </c>
+      <c r="D88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A89">
+        <f t="shared" si="0"/>
+        <v>88</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C89">
+        <v>4</v>
+      </c>
+      <c r="D89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A90">
+        <f t="shared" si="0"/>
+        <v>89</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C90">
+        <v>4</v>
+      </c>
+      <c r="D90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A91">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="C91">
+        <v>4</v>
+      </c>
+      <c r="D91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A92">
+        <f t="shared" si="0"/>
+        <v>91</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C92">
+        <v>4</v>
+      </c>
+      <c r="D92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A93">
+        <f t="shared" si="0"/>
+        <v>92</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C93">
+        <v>4</v>
+      </c>
+      <c r="D93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A94">
+        <f t="shared" si="0"/>
+        <v>93</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C94">
+        <v>4</v>
+      </c>
+      <c r="D94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A95">
+        <f t="shared" si="0"/>
+        <v>94</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C95">
+        <v>4</v>
+      </c>
+      <c r="D95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A96">
+        <f t="shared" si="0"/>
+        <v>95</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="C96">
+        <v>4</v>
+      </c>
+      <c r="D96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A97">
+        <f t="shared" si="0"/>
+        <v>96</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C97">
+        <v>4</v>
+      </c>
+      <c r="D97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A98">
+        <f t="shared" ref="A98:A161" si="1">A97+1</f>
+        <v>97</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C98">
+        <v>4</v>
+      </c>
+      <c r="D98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A99">
+        <f t="shared" si="1"/>
+        <v>98</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C99">
+        <v>4</v>
+      </c>
+      <c r="D99">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A100">
+        <f t="shared" si="1"/>
+        <v>99</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C100">
+        <v>4</v>
+      </c>
+      <c r="D100">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A101">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C101">
+        <v>4</v>
+      </c>
+      <c r="D101">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A102">
+        <f t="shared" si="1"/>
+        <v>101</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C102">
+        <v>4</v>
+      </c>
+      <c r="D102">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A103">
+        <f t="shared" si="1"/>
+        <v>102</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C103">
+        <v>4</v>
+      </c>
+      <c r="D103">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A104">
+        <f t="shared" si="1"/>
+        <v>103</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C104">
+        <v>4</v>
+      </c>
+      <c r="D104">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A105">
+        <f t="shared" si="1"/>
+        <v>104</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="C105">
+        <v>4</v>
+      </c>
+      <c r="D105">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A106">
+        <f t="shared" si="1"/>
+        <v>105</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C106">
+        <v>4</v>
+      </c>
+      <c r="D106">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A107">
+        <f t="shared" si="1"/>
+        <v>106</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C107">
+        <v>4</v>
+      </c>
+      <c r="D107">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A108">
+        <f t="shared" si="1"/>
+        <v>107</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C108">
+        <v>4</v>
+      </c>
+      <c r="D108">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A109">
+        <f t="shared" si="1"/>
+        <v>108</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C109">
+        <v>4</v>
+      </c>
+      <c r="D109">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A110">
+        <f t="shared" si="1"/>
+        <v>109</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C110">
+        <v>4</v>
+      </c>
+      <c r="D110">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A111">
+        <f t="shared" si="1"/>
+        <v>110</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C111">
+        <v>4</v>
+      </c>
+      <c r="D111">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A112">
+        <f t="shared" si="1"/>
+        <v>111</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C112">
+        <v>4</v>
+      </c>
+      <c r="D112">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A113">
+        <f t="shared" si="1"/>
+        <v>112</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C113">
+        <v>4</v>
+      </c>
+      <c r="D113">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A114">
+        <f t="shared" si="1"/>
+        <v>113</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C114">
+        <v>4</v>
+      </c>
+      <c r="D114">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A115">
+        <f t="shared" si="1"/>
+        <v>114</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C115">
+        <v>5</v>
+      </c>
+      <c r="D115">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A116">
+        <f t="shared" si="1"/>
+        <v>115</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C116">
+        <v>5</v>
+      </c>
+      <c r="D116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A117">
+        <f t="shared" si="1"/>
+        <v>116</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="C117">
+        <v>5</v>
+      </c>
+      <c r="D117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A118">
+        <f t="shared" si="1"/>
+        <v>117</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C118">
+        <v>5</v>
+      </c>
+      <c r="D118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A119">
+        <f t="shared" si="1"/>
+        <v>118</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C119">
+        <v>5</v>
+      </c>
+      <c r="D119">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A120">
+        <f t="shared" si="1"/>
+        <v>119</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C120">
+        <v>5</v>
+      </c>
+      <c r="D120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A121">
+        <f t="shared" si="1"/>
+        <v>120</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="C121">
+        <v>5</v>
+      </c>
+      <c r="D121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A122">
+        <f t="shared" si="1"/>
+        <v>121</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C122">
+        <v>5</v>
+      </c>
+      <c r="D122">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A123">
+        <f t="shared" si="1"/>
+        <v>122</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C123">
+        <v>5</v>
+      </c>
+      <c r="D123">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A124">
+        <f t="shared" si="1"/>
+        <v>123</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C124">
+        <v>5</v>
+      </c>
+      <c r="D124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A125">
+        <f t="shared" si="1"/>
+        <v>124</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C125">
+        <v>5</v>
+      </c>
+      <c r="D125">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A126">
+        <f t="shared" si="1"/>
+        <v>125</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C126">
+        <v>5</v>
+      </c>
+      <c r="D126">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A127">
+        <f t="shared" si="1"/>
+        <v>126</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C127">
+        <v>5</v>
+      </c>
+      <c r="D127">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A128">
+        <f t="shared" si="1"/>
+        <v>127</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="C128">
+        <v>5</v>
+      </c>
+      <c r="D128">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A129">
+        <f t="shared" si="1"/>
+        <v>128</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="C129">
+        <v>5</v>
+      </c>
+      <c r="D129">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A130">
+        <f t="shared" si="1"/>
+        <v>129</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C130">
+        <v>5</v>
+      </c>
+      <c r="D130">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A131">
+        <f t="shared" si="1"/>
+        <v>130</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C131">
+        <v>5</v>
+      </c>
+      <c r="D131">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A132">
+        <f t="shared" si="1"/>
+        <v>131</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="C132">
+        <v>5</v>
+      </c>
+      <c r="D132">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A133">
+        <f t="shared" si="1"/>
+        <v>132</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C133">
+        <v>5</v>
+      </c>
+      <c r="D133">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A134">
+        <f t="shared" si="1"/>
+        <v>133</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C134">
+        <v>5</v>
+      </c>
+      <c r="D134">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A135">
+        <f t="shared" si="1"/>
+        <v>134</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C135">
+        <v>5</v>
+      </c>
+      <c r="D135">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A136">
+        <f t="shared" si="1"/>
+        <v>135</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C136">
+        <v>5</v>
+      </c>
+      <c r="D136">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A137">
+        <f t="shared" si="1"/>
+        <v>136</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C137">
+        <v>5</v>
+      </c>
+      <c r="D137">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A138">
+        <f t="shared" si="1"/>
+        <v>137</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C138">
+        <v>5</v>
+      </c>
+      <c r="D138">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A139">
+        <f t="shared" si="1"/>
+        <v>138</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C139">
+        <v>5</v>
+      </c>
+      <c r="D139">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A140">
+        <f t="shared" si="1"/>
+        <v>139</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C140">
+        <v>5</v>
+      </c>
+      <c r="D140">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A141">
+        <f t="shared" si="1"/>
+        <v>140</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C141">
+        <v>5</v>
+      </c>
+      <c r="D141">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A142">
+        <f t="shared" si="1"/>
+        <v>141</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C142">
+        <v>5</v>
+      </c>
+      <c r="D142">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A143">
+        <f t="shared" si="1"/>
+        <v>142</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="C143">
+        <v>5</v>
+      </c>
+      <c r="D143">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A144">
+        <f t="shared" si="1"/>
+        <v>143</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C144">
+        <v>5</v>
+      </c>
+      <c r="D144">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A145">
+        <f t="shared" si="1"/>
+        <v>144</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C145">
+        <v>5</v>
+      </c>
+      <c r="D145">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A146">
+        <f t="shared" si="1"/>
+        <v>145</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C146">
+        <v>5</v>
+      </c>
+      <c r="D146">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A147">
+        <f t="shared" si="1"/>
+        <v>146</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C147">
+        <v>5</v>
+      </c>
+      <c r="D147">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A148">
+        <f t="shared" si="1"/>
+        <v>147</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C148">
+        <v>6</v>
+      </c>
+      <c r="D148">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A149">
+        <f t="shared" si="1"/>
+        <v>148</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C149">
+        <v>6</v>
+      </c>
+      <c r="D149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A150">
+        <f t="shared" si="1"/>
+        <v>149</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C150">
+        <v>6</v>
+      </c>
+      <c r="D150">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A151">
+        <f t="shared" si="1"/>
+        <v>150</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="C151">
+        <v>6</v>
+      </c>
+      <c r="D151">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A152">
+        <f t="shared" si="1"/>
+        <v>151</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C152">
+        <v>6</v>
+      </c>
+      <c r="D152">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A153">
+        <f t="shared" si="1"/>
+        <v>152</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C153">
+        <v>6</v>
+      </c>
+      <c r="D153">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A154">
+        <f t="shared" si="1"/>
+        <v>153</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C154">
+        <v>6</v>
+      </c>
+      <c r="D154">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A155">
+        <f t="shared" si="1"/>
+        <v>154</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C155">
+        <v>6</v>
+      </c>
+      <c r="D155">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A156">
+        <f t="shared" si="1"/>
+        <v>155</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="C156">
+        <v>6</v>
+      </c>
+      <c r="D156">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A157">
+        <f t="shared" si="1"/>
+        <v>156</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C157">
+        <v>6</v>
+      </c>
+      <c r="D157">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A158">
+        <f t="shared" si="1"/>
+        <v>157</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C158">
+        <v>6</v>
+      </c>
+      <c r="D158">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A159">
+        <f t="shared" si="1"/>
+        <v>158</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="C159">
+        <v>6</v>
+      </c>
+      <c r="D159">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A160">
+        <f t="shared" si="1"/>
+        <v>159</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C160">
+        <v>6</v>
+      </c>
+      <c r="D160">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A161">
+        <f t="shared" si="1"/>
+        <v>160</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C161">
+        <v>6</v>
+      </c>
+      <c r="D161">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A162">
+        <f t="shared" ref="A162:A225" si="2">A161+1</f>
+        <v>161</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C162">
+        <v>6</v>
+      </c>
+      <c r="D162">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A163">
+        <f t="shared" si="2"/>
+        <v>162</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="C163">
+        <v>6</v>
+      </c>
+      <c r="D163">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A164">
+        <f t="shared" si="2"/>
+        <v>163</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="C164">
+        <v>6</v>
+      </c>
+      <c r="D164">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A165">
+        <f t="shared" si="2"/>
+        <v>164</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C165">
+        <v>6</v>
+      </c>
+      <c r="D165">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A166">
+        <f t="shared" si="2"/>
+        <v>165</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="C166">
+        <v>6</v>
+      </c>
+      <c r="D166">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A167">
+        <f t="shared" si="2"/>
+        <v>166</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C167">
+        <v>6</v>
+      </c>
+      <c r="D167">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A168">
+        <f t="shared" si="2"/>
+        <v>167</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="C168">
+        <v>6</v>
+      </c>
+      <c r="D168">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A169">
+        <f t="shared" si="2"/>
+        <v>168</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="C169">
+        <v>6</v>
+      </c>
+      <c r="D169">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A170">
+        <f t="shared" si="2"/>
+        <v>169</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C170">
+        <v>6</v>
+      </c>
+      <c r="D170">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A171">
+        <f t="shared" si="2"/>
+        <v>170</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="C171">
+        <v>6</v>
+      </c>
+      <c r="D171">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A172">
+        <f t="shared" si="2"/>
+        <v>171</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C172">
+        <v>6</v>
+      </c>
+      <c r="D172">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A173">
+        <f t="shared" si="2"/>
+        <v>172</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C173">
+        <v>6</v>
+      </c>
+      <c r="D173">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A174">
+        <f t="shared" si="2"/>
+        <v>173</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C174">
+        <v>6</v>
+      </c>
+      <c r="D174">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A175">
+        <f t="shared" si="2"/>
+        <v>174</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="C175">
+        <v>6</v>
+      </c>
+      <c r="D175">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A176">
+        <f t="shared" si="2"/>
+        <v>175</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C176">
+        <v>6</v>
+      </c>
+      <c r="D176">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A177">
+        <f t="shared" si="2"/>
+        <v>176</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="C177">
+        <v>6</v>
+      </c>
+      <c r="D177">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A178">
+        <f t="shared" si="2"/>
+        <v>177</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="C178">
+        <v>6</v>
+      </c>
+      <c r="D178">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A179">
+        <f t="shared" si="2"/>
+        <v>178</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="C179">
+        <v>7</v>
+      </c>
+      <c r="D179">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A180">
+        <f t="shared" si="2"/>
+        <v>179</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="C180">
+        <v>7</v>
+      </c>
+      <c r="D180">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A181">
+        <f t="shared" si="2"/>
+        <v>180</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="C181">
+        <v>7</v>
+      </c>
+      <c r="D181">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A182">
+        <f t="shared" si="2"/>
+        <v>181</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C182">
+        <v>7</v>
+      </c>
+      <c r="D182">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A183">
+        <f t="shared" si="2"/>
+        <v>182</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="C183">
+        <v>7</v>
+      </c>
+      <c r="D183">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A184">
+        <f t="shared" si="2"/>
+        <v>183</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C184">
+        <v>7</v>
+      </c>
+      <c r="D184">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A185">
+        <f t="shared" si="2"/>
+        <v>184</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="C185">
+        <v>7</v>
+      </c>
+      <c r="D185">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A186">
+        <f t="shared" si="2"/>
+        <v>185</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="C186">
+        <v>7</v>
+      </c>
+      <c r="D186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A187">
+        <f t="shared" si="2"/>
+        <v>186</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="C187">
+        <v>7</v>
+      </c>
+      <c r="D187">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A188">
+        <f t="shared" si="2"/>
+        <v>187</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="C188">
+        <v>7</v>
+      </c>
+      <c r="D188">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A189">
+        <f t="shared" si="2"/>
+        <v>188</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C189">
+        <v>7</v>
+      </c>
+      <c r="D189">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A190">
+        <f t="shared" si="2"/>
+        <v>189</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="C190">
+        <v>7</v>
+      </c>
+      <c r="D190">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A191">
+        <f t="shared" si="2"/>
+        <v>190</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C191">
+        <v>7</v>
+      </c>
+      <c r="D191">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A192">
+        <f t="shared" si="2"/>
+        <v>191</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="C192">
+        <v>7</v>
+      </c>
+      <c r="D192">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A193">
+        <f t="shared" si="2"/>
+        <v>192</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C193">
+        <v>7</v>
+      </c>
+      <c r="D193">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A194">
+        <f t="shared" si="2"/>
+        <v>193</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="C194">
+        <v>7</v>
+      </c>
+      <c r="D194">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A195">
+        <f t="shared" si="2"/>
+        <v>194</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C195">
+        <v>7</v>
+      </c>
+      <c r="D195">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A196">
+        <f t="shared" si="2"/>
+        <v>195</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="C196">
+        <v>7</v>
+      </c>
+      <c r="D196">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A197">
+        <f t="shared" si="2"/>
+        <v>196</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="C197">
+        <v>7</v>
+      </c>
+      <c r="D197">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A198">
+        <f t="shared" si="2"/>
+        <v>197</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="C198">
+        <v>7</v>
+      </c>
+      <c r="D198">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A199">
+        <f t="shared" si="2"/>
+        <v>198</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="C199">
+        <v>7</v>
+      </c>
+      <c r="D199">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A200">
+        <f t="shared" si="2"/>
+        <v>199</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="C200">
+        <v>7</v>
+      </c>
+      <c r="D200">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A201">
+        <f t="shared" si="2"/>
+        <v>200</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="C201">
+        <v>7</v>
+      </c>
+      <c r="D201">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A202">
+        <f t="shared" si="2"/>
+        <v>201</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="C202">
+        <v>7</v>
+      </c>
+      <c r="D202">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A203">
+        <f t="shared" si="2"/>
+        <v>202</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C203">
+        <v>7</v>
+      </c>
+      <c r="D203">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A204">
+        <f t="shared" si="2"/>
+        <v>203</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="C204">
+        <v>7</v>
+      </c>
+      <c r="D204">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A205">
+        <f t="shared" si="2"/>
+        <v>204</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C205">
+        <v>8</v>
+      </c>
+      <c r="D205">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A206">
+        <f t="shared" si="2"/>
+        <v>205</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="C206">
+        <v>8</v>
+      </c>
+      <c r="D206">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A207">
+        <f t="shared" si="2"/>
+        <v>206</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="C207">
+        <v>8</v>
+      </c>
+      <c r="D207">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A208">
+        <f t="shared" si="2"/>
+        <v>207</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="C208">
+        <v>8</v>
+      </c>
+      <c r="D208">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A209">
+        <f t="shared" si="2"/>
+        <v>208</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="C209">
+        <v>8</v>
+      </c>
+      <c r="D209">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A210">
+        <f t="shared" si="2"/>
+        <v>209</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="C210">
+        <v>8</v>
+      </c>
+      <c r="D210">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A211">
+        <f t="shared" si="2"/>
+        <v>210</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="C211">
+        <v>8</v>
+      </c>
+      <c r="D211">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A212">
+        <f t="shared" si="2"/>
+        <v>211</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="C212">
+        <v>8</v>
+      </c>
+      <c r="D212">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A213">
+        <f t="shared" si="2"/>
+        <v>212</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="C213">
+        <v>8</v>
+      </c>
+      <c r="D213">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A214">
+        <f t="shared" si="2"/>
+        <v>213</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="C214">
+        <v>8</v>
+      </c>
+      <c r="D214">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A215">
+        <f t="shared" si="2"/>
+        <v>214</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="C215">
+        <v>8</v>
+      </c>
+      <c r="D215">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A216">
+        <f t="shared" si="2"/>
+        <v>215</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C216">
+        <v>8</v>
+      </c>
+      <c r="D216">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A217">
+        <f t="shared" si="2"/>
+        <v>216</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C217">
+        <v>8</v>
+      </c>
+      <c r="D217">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A218">
+        <f t="shared" si="2"/>
+        <v>217</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="C218">
+        <v>8</v>
+      </c>
+      <c r="D218">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A219">
+        <f t="shared" si="2"/>
+        <v>218</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C219">
+        <v>8</v>
+      </c>
+      <c r="D219">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A220">
+        <f t="shared" si="2"/>
+        <v>219</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="C220">
+        <v>8</v>
+      </c>
+      <c r="D220">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A221">
+        <f t="shared" si="2"/>
+        <v>220</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C221">
+        <v>8</v>
+      </c>
+      <c r="D221">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A222">
+        <f t="shared" si="2"/>
+        <v>221</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="C222">
+        <v>8</v>
+      </c>
+      <c r="D222">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A223">
+        <f t="shared" si="2"/>
+        <v>222</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C223">
+        <v>8</v>
+      </c>
+      <c r="D223">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A224">
+        <f t="shared" si="2"/>
+        <v>223</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C224">
+        <v>8</v>
+      </c>
+      <c r="D224">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A225">
+        <f t="shared" si="2"/>
+        <v>224</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="C225">
+        <v>8</v>
+      </c>
+      <c r="D225">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A226">
+        <f t="shared" ref="A226:A233" si="3">A225+1</f>
+        <v>225</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="C226">
+        <v>8</v>
+      </c>
+      <c r="D226">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A227">
+        <f t="shared" si="3"/>
+        <v>226</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C227">
+        <v>8</v>
+      </c>
+      <c r="D227">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A228">
+        <f t="shared" si="3"/>
+        <v>227</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="C228">
+        <v>8</v>
+      </c>
+      <c r="D228">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A229">
+        <f t="shared" si="3"/>
+        <v>228</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="C229">
+        <v>8</v>
+      </c>
+      <c r="D229">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A230">
+        <f t="shared" si="3"/>
+        <v>229</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="C230">
+        <v>8</v>
+      </c>
+      <c r="D230">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A231">
+        <f t="shared" si="3"/>
+        <v>230</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="C231">
+        <v>8</v>
+      </c>
+      <c r="D231">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A232">
+        <f t="shared" si="3"/>
+        <v>231</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="C232">
+        <v>8</v>
+      </c>
+      <c r="D232">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" ht="15" x14ac:dyDescent="0.35">
+      <c r="A233">
+        <f t="shared" si="3"/>
+        <v>232</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="C233">
+        <v>8</v>
+      </c>
+      <c r="D233">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>